--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486714_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486714_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4586</v>
+        <v>2.3261</v>
       </c>
       <c r="E2" t="n">
-        <v>2.0298</v>
+        <v>2.1954</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4287</v>
+        <v>0.1307</v>
       </c>
       <c r="G2" t="n">
         <v>-1.5928</v>
@@ -610,13 +610,13 @@
         <v>1.9308</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5187</v>
+        <v>0.3863</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4418</v>
+        <v>-0.2763</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9605</v>
+        <v>0.6625</v>
       </c>
       <c r="V2" t="n">
         <v>3.7257</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5916</v>
+        <v>0.1034</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0897</v>
+        <v>-0.5034</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6813</v>
+        <v>0.6068</v>
       </c>
       <c r="G3" t="n">
         <v>-0.462</v>
@@ -688,13 +688,13 @@
         <v>0.1931</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8605</v>
+        <v>0.3724</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5790999999999999</v>
+        <v>0.1654</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2814</v>
+        <v>0.2069</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.6884</v>
+        <v>-0.2125</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0461</v>
+        <v>0.0573</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6423</v>
+        <v>-0.2698</v>
       </c>
       <c r="G4" t="n">
         <v>0.5567</v>
@@ -766,13 +766,13 @@
         <v>0.9654</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8276</v>
+        <v>-0.3517</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6622</v>
+        <v>-0.5588</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1654</v>
+        <v>0.2071</v>
       </c>
       <c r="V4" t="n">
         <v>1.5133</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.0573</v>
+        <v>-0.878</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8883</v>
+        <v>0.9435</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.9456</v>
+        <v>-1.8215</v>
       </c>
       <c r="G5" t="n">
         <v>-1.0156</v>
@@ -844,13 +844,13 @@
         <v>0.5792</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7998</v>
+        <v>0.9791</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3859</v>
+        <v>0.4411</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4139</v>
+        <v>0.538</v>
       </c>
       <c r="V5" t="n">
         <v>-1.2277</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.417</v>
+        <v>-1.2376</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1792</v>
+        <v>-1.124</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2378</v>
+        <v>-0.1136</v>
       </c>
       <c r="G6" t="n">
         <v>-0.2763</v>
@@ -922,13 +922,13 @@
         <v>0.5792</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4689</v>
+        <v>-0.2896</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2759</v>
+        <v>-0.2207</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.193</v>
+        <v>-0.0689</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2856</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.4286</v>
+        <v>-1.9557</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.321</v>
+        <v>0.2513</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.1076</v>
+        <v>-2.207</v>
       </c>
       <c r="G7" t="n">
         <v>-2.2878</v>
@@ -1000,13 +1000,13 @@
         <v>0.9654</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3419</v>
+        <v>0.1311</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1036</v>
+        <v>-0.5314</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7618</v>
+        <v>0.6624</v>
       </c>
       <c r="V7" t="n">
         <v>-0.5712</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.3434</v>
+        <v>-3.7379</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.2195</v>
+        <v>-3.316</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1239</v>
+        <v>-0.4219</v>
       </c>
       <c r="G8" t="n">
         <v>-3.0072</v>
@@ -1078,13 +1078,13 @@
         <v>1.3515</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2703</v>
+        <v>-0.1241</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2211</v>
+        <v>-0.3176</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4914</v>
+        <v>0.1934</v>
       </c>
       <c r="V8" t="n">
         <v>2.8689</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. PEREZ CHAFINO</t>
+          <t>G. GUERRA LOZANO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.6224</v>
+        <v>-5.9952</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.7824</v>
+        <v>-3.035</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.84</v>
+        <v>-2.9602</v>
       </c>
       <c r="G9" t="n">
-        <v>-5.963</v>
+        <v>-0.9066</v>
       </c>
       <c r="H9" t="n">
-        <v>-4.4416</v>
+        <v>0.2418</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.5214</v>
+        <v>-1.1484</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.1821</v>
+        <v>2.4951</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.2681</v>
+        <v>3.1394</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08599999999999999</v>
+        <v>-0.6442</v>
       </c>
       <c r="M9" t="n">
-        <v>-4.7809</v>
+        <v>-3.4018</v>
       </c>
       <c r="N9" t="n">
-        <v>-3.1735</v>
+        <v>-2.8975</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.6074</v>
+        <v>-0.5042</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.7723</v>
+        <v>-4.6339</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1239</v>
+        <v>-5.9854</v>
       </c>
       <c r="R9" t="n">
         <v>1.3515</v>
       </c>
       <c r="S9" t="n">
-        <v>1.7268</v>
+        <v>-0.0413</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5236</v>
+        <v>-0.359</v>
       </c>
       <c r="U9" t="n">
-        <v>1.2032</v>
+        <v>0.3177</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6138</v>
+        <v>-0.4135</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.8142</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6138</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. GUERRA LOZANO</t>
+          <t>M. PEREZ CHAFINO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.1801</v>
+        <v>-6.2733</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.1454</v>
+        <v>-3.0857</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.0347</v>
+        <v>-3.1876</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9066</v>
+        <v>-5.963</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2418</v>
+        <v>-4.4416</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.1484</v>
+        <v>-1.5214</v>
       </c>
       <c r="J10" t="n">
-        <v>2.4951</v>
+        <v>-1.1821</v>
       </c>
       <c r="K10" t="n">
-        <v>3.1394</v>
+        <v>-1.2681</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6442</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.4018</v>
+        <v>-4.7809</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.8975</v>
+        <v>-3.1735</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5042</v>
+        <v>-1.6074</v>
       </c>
       <c r="P10" t="n">
-        <v>-4.6339</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q10" t="n">
-        <v>-5.9854</v>
+        <v>-2.1239</v>
       </c>
       <c r="R10" t="n">
         <v>1.3515</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2261</v>
+        <v>1.0758</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4693</v>
+        <v>0.2203</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2432</v>
+        <v>0.8556</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.4135</v>
+        <v>-0.6138</v>
       </c>
       <c r="W10" t="n">
-        <v>0.8142</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2277</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.7684</v>
+        <v>-6.7671</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.8455</v>
+        <v>-3.2662</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.923</v>
+        <v>-3.5008</v>
       </c>
       <c r="G11" t="n">
         <v>-4.9435</v>
@@ -1312,13 +1312,13 @@
         <v>1.3515</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3463</v>
+        <v>-0.3449</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0761</v>
+        <v>-0.4969</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2702</v>
+        <v>0.152</v>
       </c>
       <c r="V11" t="n">
         <v>-0.8995</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-25.4554</v>
+        <v>-24.6278</v>
       </c>
       <c r="E12" t="n">
-        <v>-11.7107</v>
+        <v>-10.8828</v>
       </c>
       <c r="F12" t="n">
         <v>-13.7449</v>
@@ -1360,7 +1360,7 @@
         <v>-16.5522</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.345900000000001</v>
+        <v>-3.3459</v>
       </c>
       <c r="J12" t="n">
         <v>5.664999999999999</v>
@@ -1369,7 +1369,7 @@
         <v>3.110200000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>2.555000000000001</v>
+        <v>2.555</v>
       </c>
       <c r="M12" t="n">
         <v>-25.5631</v>
@@ -1390,13 +1390,13 @@
         <v>10.6191</v>
       </c>
       <c r="S12" t="n">
-        <v>0.9652999999999998</v>
+        <v>1.7931</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.7614</v>
+        <v>-1.9339</v>
       </c>
       <c r="U12" t="n">
-        <v>3.7268</v>
+        <v>3.7267</v>
       </c>
       <c r="V12" t="n">
         <v>4.0966</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.7612</v>
+        <v>6.2342</v>
       </c>
       <c r="E13" t="n">
-        <v>1.968</v>
+        <v>2.2782</v>
       </c>
       <c r="F13" t="n">
-        <v>3.7932</v>
+        <v>3.956</v>
       </c>
       <c r="G13" t="n">
         <v>3.8755</v>
@@ -1468,13 +1468,13 @@
         <v>2.3169</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.3073</v>
+        <v>-0.8343</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1588</v>
+        <v>-0.8486</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1485</v>
+        <v>0.0142</v>
       </c>
       <c r="V13" t="n">
         <v>1.8415</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.5741</v>
+        <v>5.5451</v>
       </c>
       <c r="E14" t="n">
-        <v>4.4359</v>
+        <v>4.3324</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1382</v>
+        <v>1.2127</v>
       </c>
       <c r="G14" t="n">
         <v>3.5012</v>
@@ -1546,13 +1546,13 @@
         <v>2.3169</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6288</v>
+        <v>0.5999</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0279</v>
+        <v>-0.1313</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6567</v>
+        <v>0.7312</v>
       </c>
       <c r="V14" t="n">
         <v>0.2856</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.0341</v>
+        <v>4.6879</v>
       </c>
       <c r="E15" t="n">
-        <v>5.1054</v>
+        <v>4.7952</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0713</v>
+        <v>-0.1073</v>
       </c>
       <c r="G15" t="n">
         <v>5.567</v>
@@ -1624,13 +1624,13 @@
         <v>1.7377</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1434</v>
+        <v>-0.4896</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3038</v>
+        <v>-0.6141</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1604</v>
+        <v>0.1245</v>
       </c>
       <c r="V15" t="n">
         <v>-2.1271</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. SANCHEZ PARRA</t>
+          <t>M. MOLINA HERRERA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.5199</v>
+        <v>4.5386</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2271</v>
+        <v>2.9466</v>
       </c>
       <c r="F16" t="n">
-        <v>3.2928</v>
+        <v>1.592</v>
       </c>
       <c r="G16" t="n">
-        <v>2.0787</v>
+        <v>3.1372</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8685</v>
+        <v>3.0898</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2102</v>
+        <v>0.0475</v>
       </c>
       <c r="J16" t="n">
-        <v>1.1073</v>
+        <v>4.5659</v>
       </c>
       <c r="K16" t="n">
-        <v>1.5933</v>
+        <v>3.7113</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.486</v>
+        <v>0.8545</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9714</v>
+        <v>-1.4286</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2752</v>
+        <v>-0.6215000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>0.6962</v>
+        <v>-0.8071</v>
       </c>
       <c r="P16" t="n">
+        <v>1.1585</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-1.1585</v>
+      </c>
+      <c r="R16" t="n">
         <v>2.3169</v>
       </c>
-      <c r="Q16" t="n">
-        <v>-0.1931</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2.51</v>
-      </c>
       <c r="S16" t="n">
-        <v>0.4525</v>
+        <v>0.6138</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0273</v>
+        <v>-0.08989999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4252</v>
+        <v>0.7037</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.3282</v>
+        <v>-0.3709</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2856</v>
+        <v>-0.3709</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. MOLINA HERRERA</t>
+          <t>S. SANCHEZ PARRA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.1954</v>
+        <v>4.4054</v>
       </c>
       <c r="E17" t="n">
-        <v>2.4295</v>
+        <v>1.1237</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7658</v>
+        <v>3.2817</v>
       </c>
       <c r="G17" t="n">
-        <v>3.1372</v>
+        <v>2.0787</v>
       </c>
       <c r="H17" t="n">
-        <v>3.0898</v>
+        <v>1.8685</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0475</v>
+        <v>0.2102</v>
       </c>
       <c r="J17" t="n">
-        <v>4.5659</v>
+        <v>1.1073</v>
       </c>
       <c r="K17" t="n">
-        <v>3.7113</v>
+        <v>1.5933</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8545</v>
+        <v>-0.486</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.4286</v>
+        <v>0.9714</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6215000000000001</v>
+        <v>0.2752</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.8071</v>
+        <v>0.6962</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1585</v>
+        <v>2.3169</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1585</v>
+        <v>-0.1931</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3169</v>
+        <v>2.51</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2705</v>
+        <v>0.338</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.607</v>
+        <v>-0.0761</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.4141</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3709</v>
+        <v>-0.3282</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3709</v>
+        <v>0.2856</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.9138</v>
+        <v>3.86</v>
       </c>
       <c r="E18" t="n">
-        <v>2.1233</v>
+        <v>2.0199</v>
       </c>
       <c r="F18" t="n">
-        <v>1.7905</v>
+        <v>1.8402</v>
       </c>
       <c r="G18" t="n">
         <v>5.1136</v>
@@ -1858,13 +1858,13 @@
         <v>2.51</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3641</v>
+        <v>0.3103</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1934</v>
+        <v>-0.2969</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5575</v>
+        <v>0.6072</v>
       </c>
       <c r="V18" t="n">
         <v>-0.9847</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.7502</v>
+        <v>2.8592</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6698</v>
+        <v>1.5664</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0804</v>
+        <v>1.2928</v>
       </c>
       <c r="G19" t="n">
         <v>4.2896</v>
@@ -1936,13 +1936,13 @@
         <v>1.5446</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2538</v>
+        <v>-0.1448</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1934</v>
+        <v>-0.2969</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0603</v>
+        <v>0.152</v>
       </c>
       <c r="V19" t="n">
         <v>-0.8995</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9129</v>
+        <v>0.8053</v>
       </c>
       <c r="E20" t="n">
-        <v>0.882</v>
+        <v>0.6751</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0309</v>
+        <v>0.1302</v>
       </c>
       <c r="G20" t="n">
         <v>-1.084</v>
@@ -2014,13 +2014,13 @@
         <v>1.7377</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4523</v>
+        <v>0.3447</v>
       </c>
       <c r="T20" t="n">
-        <v>0.248</v>
+        <v>0.0412</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2042</v>
+        <v>0.3036</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0456</v>
+        <v>-0.4773</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0902</v>
+        <v>-0.8834</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0447</v>
+        <v>0.4061</v>
       </c>
       <c r="G21" t="n">
         <v>-1.3323</v>
@@ -2092,13 +2092,13 @@
         <v>1.5446</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2579</v>
+        <v>-0.6896</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7725</v>
+        <v>-0.5657</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4853</v>
+        <v>-0.1239</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.5547</v>
+        <v>-2.2693</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1301</v>
+        <v>-0.8198</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4246</v>
+        <v>-1.4494</v>
       </c>
       <c r="G22" t="n">
         <v>-1.5862</v>
@@ -2170,13 +2170,13 @@
         <v>1.9308</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7062</v>
+        <v>-0.4207</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1588</v>
+        <v>-0.8486</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4527</v>
+        <v>0.4278</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2277</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.6058</v>
+        <v>-4.0443</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.8758</v>
+        <v>-4.2894</v>
       </c>
       <c r="F23" t="n">
-        <v>0.27</v>
+        <v>0.2451</v>
       </c>
       <c r="G23" t="n">
         <v>-3.6621</v>
@@ -2248,13 +2248,13 @@
         <v>0.7723</v>
       </c>
       <c r="S23" t="n">
-        <v>0.535</v>
+        <v>0.0965</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4136</v>
+        <v>-0.0001</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1215</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="V23" t="n">
         <v>-0.2856</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>25.4555</v>
+        <v>26.1448</v>
       </c>
       <c r="E24" t="n">
-        <v>13.7449</v>
+        <v>13.74489999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>11.7106</v>
+        <v>12.4001</v>
       </c>
       <c r="G24" t="n">
         <v>19.8982</v>
@@ -2296,7 +2296,7 @@
         <v>16.5524</v>
       </c>
       <c r="I24" t="n">
-        <v>3.345900000000001</v>
+        <v>3.345899999999999</v>
       </c>
       <c r="J24" t="n">
         <v>25.5632</v>
@@ -2308,7 +2308,7 @@
         <v>5.900899999999998</v>
       </c>
       <c r="M24" t="n">
-        <v>-5.665</v>
+        <v>-5.664999999999999</v>
       </c>
       <c r="N24" t="n">
         <v>-3.1099</v>
@@ -2326,13 +2326,13 @@
         <v>21.2384</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9653999999999999</v>
+        <v>-0.2758</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.7267</v>
+        <v>-3.727</v>
       </c>
       <c r="U24" t="n">
-        <v>2.7616</v>
+        <v>3.451</v>
       </c>
       <c r="V24" t="n">
         <v>-4.0966</v>
@@ -2341,7 +2341,7 @@
         <v>2.5278</v>
       </c>
       <c r="X24" t="n">
-        <v>-6.624400000000001</v>
+        <v>-6.624399999999999</v>
       </c>
     </row>
   </sheetData>
